--- a/problems/marketing/1.youth_policy/데이터/1_정책정리표_제출용.xlsx
+++ b/problems/marketing/1.youth_policy/데이터/1_정책정리표_제출용.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정책정리" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정책정리" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>거주지요건, 연령_min/max, 취업요건, 기업규모요건, 소득상한_월_원, 연소득상한_원, 무주택요건, 학력요건, 혼인요건</t>
+          <t>거주지요건, 연령_최소/연령_최대, 취업요건, 기업규모요건, 월소득상한(원), 연소득상한(원), 무주택요건, 학력요건, 혼인요건</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>연령_min/max</t>
+          <t>연령_최소/연령_최대</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>소득상한_월_원</t>
+          <t>월소득상한(원)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>연소득상한_원</t>
+          <t>연소득상한(원)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>연령_min</t>
+          <t>연령_최소</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>연령_max</t>
+          <t>연령_최대</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>소득상한_월_원</t>
+          <t>월소득상한(원)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>연소득상한_원</t>
+          <t>연소득상한(원)</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">

--- a/problems/marketing/1.youth_policy/데이터/1_정책정리표_제출용.xlsx
+++ b/problems/marketing/1.youth_policy/데이터/1_정책정리표_제출용.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정책정리" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정책정리" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>거주지요건, 연령_최소/연령_최대, 취업요건, 기업규모요건, 월소득상한(원), 연소득상한(원), 무주택요건, 학력요건, 혼인요건</t>
+          <t>거주지요건, 연령_최소/연령_최대, 취업요건, 기업규모요건, 월소득상한(원), 월소득_중위소득기준(%), 연소득상한(원), 무주택요건, 학력요건, 혼인요건</t>
         </is>
       </c>
     </row>
@@ -560,89 +560,101 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>형식: 월 소득 상한(원, 정수). 포스터에 없으면 빈칸 (0과 빈칸은 다름). 예: 3588020</t>
+          <t>형식: 본인 월소득 절대 상한(원, 정수). 포스터에 '본인 월소득 ○○만원 이하'처럼 금액이 명시될 때만. 없으면 빈칸 (0과 빈칸은 다름). 예: 2550000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>연소득상한(원)</t>
+          <t>월소득_중위소득기준(%)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>형식: 연 소득 상한(원, 정수). 월소득과 별개 축. 포스터에 없으면 빈칸. 예: 75000000</t>
+          <t>포스터 소득요건이 '(가구) 기준 중위소득 ○○% 이하'면 그 퍼센트 숫자만 적는다. 가구원수별 실제 금액은 Part2에서 계산(2_추천리스트의 '소득기준표' 참고). 없으면 빈칸. 예: 150</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>무주택요건</t>
+          <t>연소득상한(원)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>허용값: '필요' 또는 빈칸. 예: 필요</t>
+          <t>형식: 연 소득 상한(원, 정수). 월소득과 별개 축. 포스터에 없으면 빈칸. 예: 75000000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>학력요건</t>
+          <t>무주택요건</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>허용값: '재학'(대학·대학원 재학/휴학)·'졸업'(졸업 후)·빈칸(무관). 예: 재학</t>
+          <t>허용값: '필요' 또는 빈칸. 예: 필요</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>혼인요건</t>
+          <t>학력요건</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>허용값: '신혼부부'·'미혼'·빈칸(무관). 예: 미혼</t>
+          <t>허용값: '재학'(대학·대학원 재학/휴학)·'졸업'(졸업 후)·빈칸(무관). 예: 재학</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>빈칸 규칙</t>
+          <t>혼인요건</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>빈칸 = 제약 없음(무관). 0과 빈칸은 다르다 — 무관 칸에 0이나 '무관' 글자를 넣지 말고 비운다</t>
+          <t>허용값: '신혼부부'·'미혼'·빈칸(무관). 예: 미혼</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>★확인 불가 규칙</t>
+          <t>빈칸 규칙</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>포스터에 안 나오거나 회원 명단(2_회원명단.xlsx 컬럼)으로 잴 수 없는 자격 칸은 비운다(억지 숫자=오답). 명단으로 자격을 끝까지 확인할 수 없는 정책은 Part2에서도 아무에게도 추천하지 않는다 — 확실할 때만</t>
+          <t>빈칸 = 제약 없음(무관). 0과 빈칸은 다르다 — 무관 칸에 0이나 '무관' 글자를 넣지 말고 비운다</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>★확인 불가 규칙</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>포스터에 안 나오거나 회원 명단(2_회원명단.xlsx 컬럼)으로 잴 수 없는 자격 칸은 비운다(억지 숫자=오답). 명단으로 자격을 끝까지 확인할 수 없는 정책은 Part2에서도 아무에게도 추천하지 않는다 — 확실할 때만</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>정책명·분야</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>참조용(채점 대상 아님). 이미 채워져 있음</t>
         </is>
@@ -659,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,20 +722,25 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
+          <t>월소득_중위소득기준(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
           <t>연소득상한(원)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>무주택요건</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>학력요건</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>혼인요건</t>
         </is>
@@ -755,6 +772,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -782,6 +800,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -809,6 +828,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -836,6 +856,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -863,6 +884,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -890,6 +912,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -917,6 +940,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -944,6 +968,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -971,6 +996,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
